--- a/Data/Excel_Learn/Excel_file_moi/50.xlsx
+++ b/Data/Excel_Learn/Excel_file_moi/50.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/975f0e77483dfe31/Desktop/Excel 2019/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Pareto\Khach hang\24. mos\MOS\hauwork\Source\Word_Thi\Word_Thi\bin\Debug\Zip\Enc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9741D1B8-34A2-49BF-BE7C-A7816E3A406E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5400FC32-41BF-414F-9161-198B35704BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="-30" windowWidth="20610" windowHeight="9195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="London" sheetId="1" r:id="rId1"/>
     <sheet name="New York City" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="60">
   <si>
     <t>Margie's Travel</t>
   </si>
@@ -221,8 +223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,7 +249,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="3" tint="0.399975585192419"/>
+      <color theme="3" tint="0.39994506668294322"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -324,27 +325,27 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -357,9 +358,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
@@ -392,16 +390,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="ffc6efce"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -456,7 +444,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="vi-VN"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -680,7 +668,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="vi-VN"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="204920624"/>
@@ -739,7 +727,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="vi-VN"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="204919840"/>
@@ -781,7 +769,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="vi-VN"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -811,7 +799,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="vi-VN"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1367,50 +1355,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>527997</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>59201</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>13659</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E5BE12A-35AE-4AB2-8024-11D2D4F08E4F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1919475" y="6791305"/>
-          <a:ext cx="7309694" cy="2021798"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -1441,7 +1385,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1454,10 +1398,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2" displayName="Table2" ref="A4:E21" totalsRowShown="0">
   <autoFilter ref="A4:E21" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Country or Region" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Country or Region" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="City"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Airport Code"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Air Miles" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Air Miles" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Bonus Air Miles">
       <calculatedColumnFormula>Table2[[#This Row],[Air Miles]]*0.08</calculatedColumnFormula>
     </tableColumn>
@@ -1746,18 +1690,18 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" bestFit="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.45" customHeight="1" s="7" customFormat="1">
+    <row r="1" spans="1:5" s="7" customFormat="1" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="15.75">
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
@@ -1765,24 +1709,24 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1800,224 +1744,224 @@
         <v>275.2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="2">
         <v>10600</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="2">
         <v>4780</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="2">
         <v>744</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="2">
         <v>215</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="2">
         <v>896</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="2">
         <v>11400</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="2">
         <v>5060</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="2">
         <v>1560</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" t="s">
         <v>35</v>
       </c>
       <c r="D14" s="2">
         <v>5960</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" t="s">
         <v>38</v>
       </c>
       <c r="D15" s="2">
         <v>5930</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>41</v>
       </c>
       <c r="D16" s="2">
         <v>588</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" t="s">
         <v>44</v>
       </c>
       <c r="D17" s="2">
         <v>1560</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="2">
         <v>5720</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="2">
         <v>5870</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" t="s">
         <v>52</v>
       </c>
       <c r="D20" s="2">
         <v>5530</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" t="s">
         <v>54</v>
       </c>
       <c r="D21" s="2">
@@ -2025,17 +1969,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A3:D3"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D21">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>5000</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
@@ -2049,17 +1992,17 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" bestFit="1" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" bestFit="1" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.45" customHeight="1" s="10" customFormat="1">
+    <row r="1" spans="1:4" s="10" customFormat="1" ht="26.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="15.75">
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
@@ -2067,259 +2010,259 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="2">
         <v>9940</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>49</v>
       </c>
       <c r="D6" s="2">
         <v>4750</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="2">
         <v>6830</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>46</v>
       </c>
       <c r="D8" s="2">
         <v>7370</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="2">
         <v>3620</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="2">
         <v>3950</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="2">
         <v>4260</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" t="s">
         <v>35</v>
       </c>
       <c r="D12" s="2">
         <v>6750</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="2">
         <v>2090</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="2">
         <v>8830</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" t="s">
         <v>32</v>
       </c>
       <c r="D15" s="2">
         <v>4650</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="2">
         <v>9530</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="2">
         <v>3580</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" t="s">
         <v>38</v>
       </c>
       <c r="D18" s="2">
         <v>8640</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="2">
         <v>5000</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" t="s">
         <v>58</v>
       </c>
       <c r="D20" s="2">
         <v>3440</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="2">
         <v>2410</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>59</v>
       </c>
@@ -2327,20 +2270,14 @@
       <c r="D23" s="6"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to Alo1234 under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>